--- a/dse_cutoffs_2025.xlsx
+++ b/dse_cutoffs_2025.xlsx
@@ -549,7 +549,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:T72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -568,6 +568,10 @@
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -604,28 +608,32 @@
         </is>
       </c>
       <c r="F2" s="3" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>CAP Round 2</t>
         </is>
       </c>
-      <c r="I2" s="3" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="n"/>
+      <c r="K2" s="3" t="n"/>
+      <c r="L2" s="4" t="n"/>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>CAP Round 3</t>
         </is>
       </c>
-      <c r="L2" s="3" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>CAP Round 4</t>
-        </is>
-      </c>
+      <c r="N2" s="3" t="n"/>
       <c r="O2" s="3" t="n"/>
       <c r="P2" s="4" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>CAP Round 4</t>
+        </is>
+      </c>
+      <c r="R2" s="3" t="n"/>
+      <c r="S2" s="3" t="n"/>
+      <c r="T2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="n"/>
@@ -634,60 +642,80 @@
       <c r="D3" s="5" t="n"/>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="F3" s="6" t="inlineStr">
         <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>SEBC</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="K3" s="6" t="inlineStr">
+        <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>SEBC</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>SEBC</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="S3" s="6" t="inlineStr">
         <is>
           <t>EWS</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr">
+      <c r="T3" s="6" t="inlineStr">
         <is>
           <t>SEBC</t>
         </is>
@@ -718,16 +746,14 @@
         <v>94</v>
       </c>
       <c r="F4" s="9" t="n">
+        <v>93.89</v>
+      </c>
+      <c r="G4" s="9" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="G4" s="9" t="n">
+      <c r="H4" s="9" t="n">
         <v>92</v>
       </c>
-      <c r="H4" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I4" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -764,6 +790,26 @@
         </is>
       </c>
       <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T4" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -794,16 +840,14 @@
         <v>93.16</v>
       </c>
       <c r="F5" s="12" t="n">
+        <v>92.91</v>
+      </c>
+      <c r="G5" s="12" t="n">
         <v>90.73999999999999</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="H5" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="H5" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I5" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -840,6 +884,26 @@
         </is>
       </c>
       <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T5" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -870,16 +934,14 @@
         <v>98.59</v>
       </c>
       <c r="F6" s="9" t="n">
+        <v>97.06</v>
+      </c>
+      <c r="G6" s="9" t="n">
         <v>96.56999999999999</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="H6" s="9" t="n">
         <v>97.18000000000001</v>
       </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I6" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -916,6 +978,26 @@
         </is>
       </c>
       <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T6" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -946,16 +1028,14 @@
         <v>97.40000000000001</v>
       </c>
       <c r="F7" s="12" t="n">
+        <v>96.95</v>
+      </c>
+      <c r="G7" s="12" t="n">
         <v>95.90000000000001</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="H7" s="12" t="n">
         <v>96.86</v>
       </c>
-      <c r="H7" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I7" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -992,6 +1072,26 @@
         </is>
       </c>
       <c r="P7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T7" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1022,16 +1122,14 @@
         <v>92.5</v>
       </c>
       <c r="F8" s="9" t="n">
+        <v>93.83</v>
+      </c>
+      <c r="G8" s="9" t="n">
         <v>92.29000000000001</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="H8" s="9" t="n">
         <v>92.23</v>
       </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1068,6 +1166,26 @@
         </is>
       </c>
       <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T8" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1098,16 +1216,14 @@
         <v>93.54000000000001</v>
       </c>
       <c r="F9" s="12" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="G9" s="12" t="n">
         <v>92.86</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="H9" s="12" t="n">
         <v>93.5</v>
       </c>
-      <c r="H9" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I9" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1144,6 +1260,26 @@
         </is>
       </c>
       <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T9" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1174,16 +1310,14 @@
         <v>93.77</v>
       </c>
       <c r="F10" s="9" t="n">
+        <v>93.54000000000001</v>
+      </c>
+      <c r="G10" s="9" t="n">
         <v>92.17</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="H10" s="9" t="n">
         <v>92.63</v>
       </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I10" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1220,6 +1354,26 @@
         </is>
       </c>
       <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T10" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1250,16 +1404,14 @@
         <v>95.66</v>
       </c>
       <c r="F11" s="12" t="n">
+        <v>95.42</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <v>96.34</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>95.63</v>
       </c>
-      <c r="H11" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I11" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1296,6 +1448,26 @@
         </is>
       </c>
       <c r="P11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T11" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1326,16 +1498,14 @@
         <v>95.26000000000001</v>
       </c>
       <c r="F12" s="9" t="n">
+        <v>95.18000000000001</v>
+      </c>
+      <c r="G12" s="9" t="n">
         <v>95.03</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="H12" s="9" t="n">
         <v>95.26000000000001</v>
       </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I12" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1372,6 +1542,26 @@
         </is>
       </c>
       <c r="P12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T12" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1402,16 +1592,14 @@
         <v>95.26000000000001</v>
       </c>
       <c r="F13" s="12" t="n">
+        <v>95.2</v>
+      </c>
+      <c r="G13" s="12" t="n">
         <v>94.63</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>95.2</v>
       </c>
-      <c r="H13" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I13" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1448,6 +1636,26 @@
         </is>
       </c>
       <c r="P13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T13" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1478,16 +1686,14 @@
         <v>95.2</v>
       </c>
       <c r="F14" s="9" t="n">
+        <v>95.13</v>
+      </c>
+      <c r="G14" s="9" t="n">
         <v>94.17</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="H14" s="9" t="n">
         <v>95.2</v>
       </c>
-      <c r="H14" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1524,6 +1730,26 @@
         </is>
       </c>
       <c r="P14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T14" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1554,16 +1780,14 @@
         <v>95.88</v>
       </c>
       <c r="F15" s="12" t="n">
+        <v>95.09</v>
+      </c>
+      <c r="G15" s="12" t="n">
         <v>94.18000000000001</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>95.26000000000001</v>
       </c>
-      <c r="H15" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I15" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1600,6 +1824,26 @@
         </is>
       </c>
       <c r="P15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T15" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1630,16 +1874,14 @@
         <v>92.17</v>
       </c>
       <c r="F16" s="9" t="n">
+        <v>90.69</v>
+      </c>
+      <c r="G16" s="9" t="n">
         <v>86.8</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="H16" s="9" t="n">
         <v>92.56999999999999</v>
       </c>
-      <c r="H16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I16" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1676,6 +1918,26 @@
         </is>
       </c>
       <c r="P16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T16" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1706,16 +1968,14 @@
         <v>92.11</v>
       </c>
       <c r="F17" s="12" t="n">
+        <v>89.31</v>
+      </c>
+      <c r="G17" s="12" t="n">
         <v>86.18000000000001</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I17" s="10" t="inlineStr">
         <is>
           <t>-</t>
@@ -1752,6 +2012,26 @@
         </is>
       </c>
       <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T17" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1782,16 +2062,14 @@
         <v>83.48</v>
       </c>
       <c r="F18" s="9" t="n">
+        <v>80.62</v>
+      </c>
+      <c r="G18" s="9" t="n">
         <v>70.22</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="H18" s="9" t="n">
         <v>79.41</v>
       </c>
-      <c r="H18" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="I18" s="7" t="inlineStr">
         <is>
           <t>-</t>
@@ -1828,6 +2106,26 @@
         </is>
       </c>
       <c r="P18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T18" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1836,17 +2134,17 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="B19" s="11" t="inlineStr">
         <is>
-          <t>JSPMS Jaywantrao Sawant College of Engineering,Pune</t>
+          <t>Jaywant Shikshan Prasarak Mandals,Rajarshi Shahu College of Engineering, Tathawade, Pune</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
         <is>
-          <t>614524510</t>
+          <t>614124510</t>
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr">
@@ -1855,18 +2153,16 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>90.73999999999999</v>
+        <v>92.47</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>85.25</v>
+        <v>92</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>90.29000000000001</v>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.34</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>92.17</v>
       </c>
       <c r="I19" s="10" t="inlineStr">
         <is>
@@ -1904,6 +2200,26 @@
         </is>
       </c>
       <c r="P19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T19" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1912,17 +2228,17 @@
     <row r="20">
       <c r="A20" s="7" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>JSPMS Jaywantrao Sawant College of Engineering,Pune</t>
+          <t>Jaywant Shikshan Prasarak Mandals,Rajarshi Shahu College of Engineering, Tathawade, Pune</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>614524610</t>
+          <t>614124610</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
@@ -1931,18 +2247,16 @@
         </is>
       </c>
       <c r="E20" s="9" t="n">
-        <v>90.19</v>
+        <v>92.11</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>84.86</v>
+        <v>92</v>
       </c>
       <c r="G20" s="9" t="n">
-        <v>90.11</v>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>92.06</v>
       </c>
       <c r="I20" s="7" t="inlineStr">
         <is>
@@ -1980,6 +2294,26 @@
         </is>
       </c>
       <c r="P20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T20" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -1988,37 +2322,35 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>6145</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="B21" s="11" t="inlineStr">
         <is>
-          <t>JSPMS Jaywantrao Sawant College of Engineering,Pune</t>
+          <t>Jaywant Shikshan Prasarak Mandals,Rajarshi Shahu College of Engineering, Tathawade, Pune</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
         <is>
-          <t>614526310</t>
+          <t>614126210</t>
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) and Data Science</t>
+          <t>Computer Science and Business Systems</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>90</v>
+        <v>91.44</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>88.23</v>
+        <v>91.37</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>90.5</v>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.69</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>91.13</v>
       </c>
       <c r="I21" s="10" t="inlineStr">
         <is>
@@ -2056,6 +2388,26 @@
         </is>
       </c>
       <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T21" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2064,37 +2416,35 @@
     <row r="22">
       <c r="A22" s="7" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6141</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>MIT Academy of Engineering,Alandi, Pune</t>
+          <t>Jaywant Shikshan Prasarak Mandals,Rajarshi Shahu College of Engineering, Tathawade, Pune</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>614624510</t>
+          <t>614191610</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>Computer Engineering</t>
+          <t>Automation and Robotics</t>
         </is>
       </c>
       <c r="E22" s="9" t="n">
-        <v>92.23</v>
+        <v>88.44</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>89.70999999999999</v>
+        <v>88.06</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>92.11</v>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>85.14</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>87.77</v>
       </c>
       <c r="I22" s="7" t="inlineStr">
         <is>
@@ -2132,6 +2482,26 @@
         </is>
       </c>
       <c r="P22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T22" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2140,37 +2510,35 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="B23" s="11" t="inlineStr">
         <is>
-          <t>MIT Academy of Engineering,Alandi, Pune</t>
+          <t>JSPMS Jaywantrao Sawant College of Engineering,Pune</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
         <is>
-          <t>614624610</t>
+          <t>614524510</t>
         </is>
       </c>
       <c r="D23" s="10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>92</v>
+        <v>90.73999999999999</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>89.48999999999999</v>
+        <v>90.63</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>85.25</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>90.29000000000001</v>
       </c>
       <c r="I23" s="10" t="inlineStr">
         <is>
@@ -2208,6 +2576,26 @@
         </is>
       </c>
       <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T23" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2216,37 +2604,35 @@
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>MIT Academy of Engineering,Alandi, Pune</t>
+          <t>JSPMS Jaywantrao Sawant College of Engineering,Pune</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>614691110</t>
+          <t>614524610</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E24" s="9" t="n">
-        <v>91.83</v>
+        <v>90.19</v>
       </c>
       <c r="F24" s="9" t="n">
-        <v>90.33</v>
+        <v>90.17</v>
       </c>
       <c r="G24" s="9" t="n">
-        <v>91.66</v>
-      </c>
-      <c r="H24" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>84.86</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <v>90.11</v>
       </c>
       <c r="I24" s="7" t="inlineStr">
         <is>
@@ -2284,6 +2670,26 @@
         </is>
       </c>
       <c r="P24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T24" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2292,37 +2698,35 @@
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>6146</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="B25" s="11" t="inlineStr">
         <is>
-          <t>MIT Academy of Engineering,Alandi, Pune</t>
+          <t>JSPMS Jaywantrao Sawant College of Engineering,Pune</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
         <is>
-          <t>614691210</t>
+          <t>614526310</t>
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Data Science)</t>
+          <t>Artificial Intelligence (AI) and Data Science</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>91.73999999999999</v>
+        <v>90</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>88.29000000000001</v>
+        <v>89.94</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>91.13</v>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.23</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>90.5</v>
       </c>
       <c r="I25" s="10" t="inlineStr">
         <is>
@@ -2360,6 +2764,26 @@
         </is>
       </c>
       <c r="P25" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q25" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T25" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2378,27 +2802,25 @@
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>614692710</t>
+          <t>614624510</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>Computer Engineering (Software Engineering)</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E26" s="9" t="n">
-        <v>91.59999999999999</v>
+        <v>92.23</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>88.8</v>
+        <v>91.94</v>
       </c>
       <c r="G26" s="9" t="n">
-        <v>91.14</v>
-      </c>
-      <c r="H26" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.70999999999999</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <v>92.11</v>
       </c>
       <c r="I26" s="7" t="inlineStr">
         <is>
@@ -2436,6 +2858,26 @@
         </is>
       </c>
       <c r="P26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T26" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2444,37 +2886,35 @@
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="B27" s="11" t="inlineStr">
         <is>
-          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
+          <t>MIT Academy of Engineering,Alandi, Pune</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
         <is>
-          <t>617524510</t>
+          <t>614624610</t>
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr">
         <is>
-          <t>Computer Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>94.63</v>
+        <v>92</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>94</v>
+        <v>92.13</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>94.51000000000001</v>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.48999999999999</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>92</v>
       </c>
       <c r="I27" s="10" t="inlineStr">
         <is>
@@ -2512,6 +2952,26 @@
         </is>
       </c>
       <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T27" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2520,37 +2980,35 @@
     <row r="28">
       <c r="A28" s="7" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
+          <t>MIT Academy of Engineering,Alandi, Pune</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>617524590</t>
+          <t>614691110</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>Computer Engineering</t>
+          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
         </is>
       </c>
       <c r="E28" s="9" t="n">
-        <v>94.29000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>92.70999999999999</v>
+        <v>91.81</v>
       </c>
       <c r="G28" s="9" t="n">
-        <v>94.29000000000001</v>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.33</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <v>91.66</v>
       </c>
       <c r="I28" s="7" t="inlineStr">
         <is>
@@ -2588,6 +3046,26 @@
         </is>
       </c>
       <c r="P28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T28" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2596,37 +3074,35 @@
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="B29" s="11" t="inlineStr">
         <is>
-          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
+          <t>MIT Academy of Engineering,Alandi, Pune</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
         <is>
-          <t>617524610</t>
+          <t>614691210</t>
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Science and Engineering(Data Science)</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>94.23999999999999</v>
+        <v>91.73999999999999</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>93.31</v>
+        <v>91.61</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>94.06</v>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.29000000000001</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>91.13</v>
       </c>
       <c r="I29" s="10" t="inlineStr">
         <is>
@@ -2664,6 +3140,26 @@
         </is>
       </c>
       <c r="P29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T29" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2672,37 +3168,35 @@
     <row r="30">
       <c r="A30" s="7" t="inlineStr">
         <is>
-          <t>6175</t>
+          <t>6146</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
+          <t>MIT Academy of Engineering,Alandi, Pune</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>617591110</t>
+          <t>614692710</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
+          <t>Computer Engineering (Software Engineering)</t>
         </is>
       </c>
       <c r="E30" s="9" t="n">
-        <v>94.78</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="F30" s="9" t="n">
-        <v>92.23</v>
+        <v>91.31</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>94.17</v>
-      </c>
-      <c r="H30" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.8</v>
+      </c>
+      <c r="H30" s="9" t="n">
+        <v>91.14</v>
       </c>
       <c r="I30" s="7" t="inlineStr">
         <is>
@@ -2740,6 +3234,26 @@
         </is>
       </c>
       <c r="P30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T30" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2748,17 +3262,17 @@
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="B31" s="11" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
+          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
         <is>
-          <t>620724510</t>
+          <t>617524510</t>
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr">
@@ -2767,18 +3281,16 @@
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>93</v>
+        <v>94.63</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>90.29000000000001</v>
+        <v>94.47</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>94</v>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>94.51000000000001</v>
       </c>
       <c r="I31" s="10" t="inlineStr">
         <is>
@@ -2816,6 +3328,26 @@
         </is>
       </c>
       <c r="P31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T31" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2824,37 +3356,35 @@
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
+          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>620724610</t>
+          <t>617524590</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E32" s="9" t="n">
-        <v>92.59</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="F32" s="9" t="n">
-        <v>90.29000000000001</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>92.56</v>
-      </c>
-      <c r="H32" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>92.70999999999999</v>
+      </c>
+      <c r="H32" s="9" t="n">
+        <v>94.29000000000001</v>
       </c>
       <c r="I32" s="7" t="inlineStr">
         <is>
@@ -2892,6 +3422,26 @@
         </is>
       </c>
       <c r="P32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T32" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2900,37 +3450,35 @@
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="B33" s="11" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
+          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
         </is>
       </c>
       <c r="C33" s="10" t="inlineStr">
         <is>
-          <t>620791610</t>
+          <t>617524610</t>
         </is>
       </c>
       <c r="D33" s="10" t="inlineStr">
         <is>
-          <t>Automation and Robotics</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>90.53</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>84.13</v>
+        <v>94.11</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>86.97</v>
-      </c>
-      <c r="H33" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>93.31</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>94.06</v>
       </c>
       <c r="I33" s="10" t="inlineStr">
         <is>
@@ -2968,6 +3516,26 @@
         </is>
       </c>
       <c r="P33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T33" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -2976,37 +3544,35 @@
     <row r="34">
       <c r="A34" s="7" t="inlineStr">
         <is>
-          <t>6207</t>
+          <t>6175</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
+          <t>Pimpri Chinchwad Education Trust, Pimpri Chinchwad College of Engineering, Pune</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>620799510</t>
+          <t>617591110</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence and Data Science</t>
+          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
         </is>
       </c>
       <c r="E34" s="9" t="n">
-        <v>92.29000000000001</v>
+        <v>94.78</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>89.17</v>
+        <v>93.83</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>92.28</v>
-      </c>
-      <c r="H34" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>92.23</v>
+      </c>
+      <c r="H34" s="9" t="n">
+        <v>94.17</v>
       </c>
       <c r="I34" s="7" t="inlineStr">
         <is>
@@ -3044,6 +3610,26 @@
         </is>
       </c>
       <c r="P34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T34" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3052,37 +3638,35 @@
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="B35" s="11" t="inlineStr">
         <is>
-          <t>D.Y. Patil College of Engineering and Technology, Kolhapur</t>
+          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
         </is>
       </c>
       <c r="C35" s="10" t="inlineStr">
         <is>
-          <t>625024210</t>
+          <t>620724510</t>
         </is>
       </c>
       <c r="D35" s="10" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>90.83</v>
+        <v>93</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>88.97</v>
+        <v>92.63</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>90.34</v>
-      </c>
-      <c r="H35" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.29000000000001</v>
+      </c>
+      <c r="H35" s="12" t="n">
+        <v>92.87</v>
       </c>
       <c r="I35" s="10" t="inlineStr">
         <is>
@@ -3120,6 +3704,26 @@
         </is>
       </c>
       <c r="P35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T35" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3128,37 +3732,35 @@
     <row r="36">
       <c r="A36" s="7" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>D.Y. Patil College of Engineering and Technology, Kolhapur</t>
+          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>625091110</t>
+          <t>620724610</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E36" s="9" t="n">
-        <v>89.89</v>
+        <v>92.59</v>
       </c>
       <c r="F36" s="9" t="n">
-        <v>85.48999999999999</v>
+        <v>92.53</v>
       </c>
       <c r="G36" s="9" t="n">
-        <v>89.70999999999999</v>
-      </c>
-      <c r="H36" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.29000000000001</v>
+      </c>
+      <c r="H36" s="9" t="n">
+        <v>92.56</v>
       </c>
       <c r="I36" s="7" t="inlineStr">
         <is>
@@ -3196,6 +3798,26 @@
         </is>
       </c>
       <c r="P36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T36" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3204,37 +3826,35 @@
     <row r="37">
       <c r="A37" s="10" t="inlineStr">
         <is>
-          <t>6250</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="B37" s="11" t="inlineStr">
         <is>
-          <t>D.Y. Patil College of Engineering and Technology, Kolhapur</t>
+          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
         </is>
       </c>
       <c r="C37" s="10" t="inlineStr">
         <is>
-          <t>625091210</t>
+          <t>620791610</t>
         </is>
       </c>
       <c r="D37" s="10" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Data Science)</t>
+          <t>Automation and Robotics</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>89.48999999999999</v>
+        <v>90.53</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>84.86</v>
+        <v>90.13</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>89.48999999999999</v>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>84.13</v>
+      </c>
+      <c r="H37" s="12" t="n">
+        <v>86.97</v>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
@@ -3272,6 +3892,26 @@
         </is>
       </c>
       <c r="P37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T37" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3280,41 +3920,35 @@
     <row r="38">
       <c r="A38" s="7" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6207</t>
         </is>
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Walchand Institute of Technology, Solapur</t>
+          <t>Dr. D. Y. Patil Unitech Societys Dr. D. Y. Patil Institute of Technology, Pimpri, Pune</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>626524210</t>
+          <t>620799510</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Artificial Intelligence and Data Science</t>
         </is>
       </c>
       <c r="E38" s="9" t="n">
-        <v>92.38</v>
-      </c>
-      <c r="F38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>92.29000000000001</v>
+      </c>
+      <c r="F38" s="9" t="n">
+        <v>92.18000000000001</v>
+      </c>
+      <c r="G38" s="9" t="n">
+        <v>89.17</v>
+      </c>
+      <c r="H38" s="9" t="n">
+        <v>92.28</v>
       </c>
       <c r="I38" s="7" t="inlineStr">
         <is>
@@ -3352,6 +3986,26 @@
         </is>
       </c>
       <c r="P38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T38" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3360,41 +4014,35 @@
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="B39" s="11" t="inlineStr">
         <is>
-          <t>Walchand Institute of Technology, Solapur</t>
+          <t>D.Y. Patil College of Engineering and Technology, Kolhapur</t>
         </is>
       </c>
       <c r="C39" s="10" t="inlineStr">
         <is>
-          <t>626524610</t>
+          <t>625024210</t>
         </is>
       </c>
       <c r="D39" s="10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>91.37</v>
-      </c>
-      <c r="F39" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G39" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.83</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>88.97</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>90.34</v>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
@@ -3432,6 +4080,26 @@
         </is>
       </c>
       <c r="P39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T39" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3440,41 +4108,35 @@
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Walchand Institute of Technology, Solapur</t>
+          <t>D.Y. Patil College of Engineering and Technology, Kolhapur</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>626561510</t>
+          <t>625091110</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>Mechanical &amp; Automation Engineering</t>
+          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
         </is>
       </c>
       <c r="E40" s="9" t="n">
-        <v>81.48999999999999</v>
-      </c>
-      <c r="F40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>89.89</v>
+      </c>
+      <c r="F40" s="9" t="n">
+        <v>88.8</v>
+      </c>
+      <c r="G40" s="9" t="n">
+        <v>85.48999999999999</v>
+      </c>
+      <c r="H40" s="9" t="n">
+        <v>89.70999999999999</v>
       </c>
       <c r="I40" s="7" t="inlineStr">
         <is>
@@ -3512,6 +4174,26 @@
         </is>
       </c>
       <c r="P40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T40" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3520,41 +4202,35 @@
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t>6265</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="B41" s="11" t="inlineStr">
         <is>
-          <t>Walchand Institute of Technology, Solapur</t>
+          <t>D.Y. Patil College of Engineering and Technology, Kolhapur</t>
         </is>
       </c>
       <c r="C41" s="10" t="inlineStr">
         <is>
-          <t>626584410</t>
+          <t>625091210</t>
         </is>
       </c>
       <c r="D41" s="10" t="inlineStr">
         <is>
-          <t>Electronics and Computer Engineering</t>
+          <t>Computer Science and Engineering(Data Science)</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
         <v>89.48999999999999</v>
       </c>
-      <c r="F41" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G41" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F41" s="12" t="n">
+        <v>88.63</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>89.48999999999999</v>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
@@ -3592,6 +4268,26 @@
         </is>
       </c>
       <c r="P41" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q41" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T41" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3600,17 +4296,17 @@
     <row r="42">
       <c r="A42" s="7" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Kolhapur Institute of Technology's College of Engineering(Autonomous), Kolhapur</t>
+          <t>Walchand Institute of Technology, Solapur</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>626724210</t>
+          <t>626524210</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
@@ -3619,13 +4315,17 @@
         </is>
       </c>
       <c r="E42" s="9" t="n">
-        <v>93.26000000000001</v>
-      </c>
-      <c r="F42" s="9" t="n">
-        <v>92.56999999999999</v>
-      </c>
-      <c r="G42" s="9" t="n">
-        <v>93.14</v>
+        <v>92.38</v>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
         <is>
@@ -3668,6 +4368,26 @@
         </is>
       </c>
       <c r="P42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T42" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3676,32 +4396,36 @@
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="B43" s="11" t="inlineStr">
         <is>
-          <t>Kolhapur Institute of Technology's College of Engineering(Autonomous), Kolhapur</t>
+          <t>Walchand Institute of Technology, Solapur</t>
         </is>
       </c>
       <c r="C43" s="10" t="inlineStr">
         <is>
-          <t>626726210</t>
+          <t>626524610</t>
         </is>
       </c>
       <c r="D43" s="10" t="inlineStr">
         <is>
-          <t>Computer Science and Business Systems</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>90.34</v>
-      </c>
-      <c r="F43" s="12" t="n">
-        <v>88.29000000000001</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>90.27</v>
+        <v>91.37</v>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
@@ -3744,6 +4468,26 @@
         </is>
       </c>
       <c r="P43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T43" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3752,32 +4496,36 @@
     <row r="44">
       <c r="A44" s="7" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Kolhapur Institute of Technology's College of Engineering(Autonomous), Kolhapur</t>
+          <t>Walchand Institute of Technology, Solapur</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>626791110</t>
+          <t>626561510</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
+          <t>Mechanical &amp; Automation Engineering</t>
         </is>
       </c>
       <c r="E44" s="9" t="n">
-        <v>92.06</v>
-      </c>
-      <c r="F44" s="9" t="n">
-        <v>90.67</v>
-      </c>
-      <c r="G44" s="9" t="n">
-        <v>91.66</v>
+        <v>81.48999999999999</v>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
         <is>
@@ -3820,6 +4568,26 @@
         </is>
       </c>
       <c r="P44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T44" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3828,32 +4596,36 @@
     <row r="45">
       <c r="A45" s="10" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6265</t>
         </is>
       </c>
       <c r="B45" s="11" t="inlineStr">
         <is>
-          <t>Pune Institute of Computer Technology</t>
+          <t>Walchand Institute of Technology, Solapur</t>
         </is>
       </c>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>627124510</t>
+          <t>626584410</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
         <is>
-          <t>Computer Engineering</t>
+          <t>Electronics and Computer Engineering</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="F45" s="12" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>96.08</v>
+        <v>89.48999999999999</v>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H45" s="10" t="inlineStr">
         <is>
@@ -3896,6 +4668,26 @@
         </is>
       </c>
       <c r="P45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T45" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3904,37 +4696,35 @@
     <row r="46">
       <c r="A46" s="7" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>Pune Institute of Computer Technology</t>
+          <t>Kolhapur Institute of Technology's College of Engineering(Autonomous), Kolhapur</t>
         </is>
       </c>
       <c r="C46" s="7" t="inlineStr">
         <is>
-          <t>627124610</t>
+          <t>626724210</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E46" s="9" t="n">
-        <v>95.89</v>
+        <v>93.26000000000001</v>
       </c>
       <c r="F46" s="9" t="n">
-        <v>95.09</v>
+        <v>92.56999999999999</v>
       </c>
       <c r="G46" s="9" t="n">
-        <v>95.66</v>
-      </c>
-      <c r="H46" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>92.56999999999999</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>93.14</v>
       </c>
       <c r="I46" s="7" t="inlineStr">
         <is>
@@ -3972,6 +4762,26 @@
         </is>
       </c>
       <c r="P46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T46" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3980,37 +4790,35 @@
     <row r="47">
       <c r="A47" s="10" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>Pune Institute of Computer Technology</t>
+          <t>Kolhapur Institute of Technology's College of Engineering(Autonomous), Kolhapur</t>
         </is>
       </c>
       <c r="C47" s="10" t="inlineStr">
         <is>
-          <t>627126310</t>
+          <t>626726210</t>
         </is>
       </c>
       <c r="D47" s="10" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) and Data Science</t>
+          <t>Computer Science and Business Systems</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>95.83</v>
+        <v>90.34</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>95.23999999999999</v>
+        <v>89.77</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>95.59999999999999</v>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.29000000000001</v>
+      </c>
+      <c r="H47" s="12" t="n">
+        <v>90.27</v>
       </c>
       <c r="I47" s="10" t="inlineStr">
         <is>
@@ -4048,6 +4856,26 @@
         </is>
       </c>
       <c r="P47" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q47" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R47" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T47" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4056,37 +4884,35 @@
     <row r="48">
       <c r="A48" s="7" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Pune Institute of Computer Technology</t>
+          <t>Kolhapur Institute of Technology's College of Engineering(Autonomous), Kolhapur</t>
         </is>
       </c>
       <c r="C48" s="7" t="inlineStr">
         <is>
-          <t>627184410</t>
+          <t>626791110</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>Electronics and Computer Engineering</t>
+          <t>Computer Science and Engineering(Artificial Intelligence and Machine Learning)</t>
         </is>
       </c>
       <c r="E48" s="9" t="n">
-        <v>95.26000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>93.26000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="G48" s="9" t="n">
-        <v>95.14</v>
-      </c>
-      <c r="H48" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90.67</v>
+      </c>
+      <c r="H48" s="9" t="n">
+        <v>91.66</v>
       </c>
       <c r="I48" s="7" t="inlineStr">
         <is>
@@ -4124,6 +4950,26 @@
         </is>
       </c>
       <c r="P48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T48" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4132,37 +4978,35 @@
     <row r="49">
       <c r="A49" s="10" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
+          <t>Rayat Shikshan Sansthas Karmaveer Bhaurao Patil College of Engineering, Satara</t>
         </is>
       </c>
       <c r="C49" s="10" t="inlineStr">
         <is>
-          <t>627221910</t>
+          <t>627024210</t>
         </is>
       </c>
       <c r="D49" s="10" t="inlineStr">
         <is>
-          <t>Robotics and Automation</t>
+          <t>Computer Science and Engineering</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>90.19</v>
+        <v>86.38</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>86.69</v>
+        <v>84.17</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>89.83</v>
-      </c>
-      <c r="H49" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>73.48999999999999</v>
+      </c>
+      <c r="H49" s="12" t="n">
+        <v>86.34</v>
       </c>
       <c r="I49" s="10" t="inlineStr">
         <is>
@@ -4200,6 +5044,26 @@
         </is>
       </c>
       <c r="P49" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q49" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R49" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T49" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4208,37 +5072,35 @@
     <row r="50">
       <c r="A50" s="7" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
+          <t>Rayat Shikshan Sansthas Karmaveer Bhaurao Patil College of Engineering, Satara</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>627224510</t>
+          <t>627099510</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>Computer Engineering</t>
+          <t>Artificial Intelligence and Data Science</t>
         </is>
       </c>
       <c r="E50" s="9" t="n">
-        <v>93.70999999999999</v>
+        <v>84.17</v>
       </c>
       <c r="F50" s="9" t="n">
-        <v>92.34</v>
+        <v>83.44</v>
       </c>
       <c r="G50" s="9" t="n">
-        <v>93.44</v>
-      </c>
-      <c r="H50" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>76.45999999999999</v>
+      </c>
+      <c r="H50" s="9" t="n">
+        <v>84.69</v>
       </c>
       <c r="I50" s="7" t="inlineStr">
         <is>
@@ -4276,6 +5138,26 @@
         </is>
       </c>
       <c r="P50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T50" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4284,37 +5166,35 @@
     <row r="51">
       <c r="A51" s="10" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
+          <t>Pune Institute of Computer Technology</t>
         </is>
       </c>
       <c r="C51" s="10" t="inlineStr">
         <is>
-          <t>627224610</t>
+          <t>627124510</t>
         </is>
       </c>
       <c r="D51" s="10" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>93.2</v>
+        <v>96.31</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>91.83</v>
+        <v>96.29000000000001</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>92.75</v>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>95.59999999999999</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>96.08</v>
       </c>
       <c r="I51" s="10" t="inlineStr">
         <is>
@@ -4352,6 +5232,26 @@
         </is>
       </c>
       <c r="P51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T51" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4360,37 +5260,35 @@
     <row r="52">
       <c r="A52" s="7" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
+          <t>Pune Institute of Computer Technology</t>
         </is>
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>627299510</t>
+          <t>627124610</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence and Data Science</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E52" s="9" t="n">
-        <v>92.59999999999999</v>
+        <v>95.89</v>
       </c>
       <c r="F52" s="9" t="n">
-        <v>91.41</v>
+        <v>95.77</v>
       </c>
       <c r="G52" s="9" t="n">
-        <v>92.40000000000001</v>
-      </c>
-      <c r="H52" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>95.09</v>
+      </c>
+      <c r="H52" s="9" t="n">
+        <v>95.66</v>
       </c>
       <c r="I52" s="7" t="inlineStr">
         <is>
@@ -4428,6 +5326,26 @@
         </is>
       </c>
       <c r="P52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T52" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4436,37 +5354,35 @@
     <row r="53">
       <c r="A53" s="10" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>International Institute of Information Technology (I²IT), Pune.</t>
+          <t>Pune Institute of Computer Technology</t>
         </is>
       </c>
       <c r="C53" s="10" t="inlineStr">
         <is>
-          <t>675424510</t>
+          <t>627126310</t>
         </is>
       </c>
       <c r="D53" s="10" t="inlineStr">
         <is>
-          <t>Computer Engineering</t>
+          <t>Artificial Intelligence (AI) and Data Science</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>91.77</v>
+        <v>95.83</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>90.40000000000001</v>
+        <v>95.77</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>91.66</v>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>95.23999999999999</v>
+      </c>
+      <c r="H53" s="12" t="n">
+        <v>95.59999999999999</v>
       </c>
       <c r="I53" s="10" t="inlineStr">
         <is>
@@ -4504,6 +5420,26 @@
         </is>
       </c>
       <c r="P53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T53" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4512,37 +5448,35 @@
     <row r="54">
       <c r="A54" s="7" t="inlineStr">
         <is>
-          <t>6754</t>
+          <t>6271</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>International Institute of Information Technology (I²IT), Pune.</t>
+          <t>Pune Institute of Computer Technology</t>
         </is>
       </c>
       <c r="C54" s="7" t="inlineStr">
         <is>
-          <t>675424610</t>
+          <t>627184410</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>Information Technology</t>
+          <t>Electronics and Computer Engineering</t>
         </is>
       </c>
       <c r="E54" s="9" t="n">
-        <v>91.48999999999999</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>88.97</v>
+        <v>94.93000000000001</v>
       </c>
       <c r="G54" s="9" t="n">
-        <v>91.37</v>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>93.26000000000001</v>
+      </c>
+      <c r="H54" s="9" t="n">
+        <v>95.14</v>
       </c>
       <c r="I54" s="7" t="inlineStr">
         <is>
@@ -4580,6 +5514,26 @@
         </is>
       </c>
       <c r="P54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T54" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4588,37 +5542,35 @@
     <row r="55">
       <c r="A55" s="10" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>JSPM Narhe Technical Campus, Pune.</t>
+          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
         </is>
       </c>
       <c r="C55" s="10" t="inlineStr">
         <is>
-          <t>675524510</t>
+          <t>627221910</t>
         </is>
       </c>
       <c r="D55" s="10" t="inlineStr">
         <is>
-          <t>Computer Engineering</t>
+          <t>Robotics and Automation</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>90</v>
+        <v>90.19</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>84.38</v>
+        <v>89.88</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>89.76000000000001</v>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>86.69</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>89.83</v>
       </c>
       <c r="I55" s="10" t="inlineStr">
         <is>
@@ -4656,6 +5608,26 @@
         </is>
       </c>
       <c r="P55" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q55" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R55" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T55" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4664,37 +5636,35 @@
     <row r="56">
       <c r="A56" s="7" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>JSPM Narhe Technical Campus, Pune.</t>
+          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
         </is>
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>675526310</t>
+          <t>627224510</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>Artificial Intelligence (AI) and Data Science</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E56" s="9" t="n">
-        <v>89.26000000000001</v>
+        <v>93.70999999999999</v>
       </c>
       <c r="F56" s="9" t="n">
-        <v>83.47</v>
+        <v>93.31</v>
       </c>
       <c r="G56" s="9" t="n">
-        <v>89.09</v>
-      </c>
-      <c r="H56" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>92.34</v>
+      </c>
+      <c r="H56" s="9" t="n">
+        <v>93.44</v>
       </c>
       <c r="I56" s="7" t="inlineStr">
         <is>
@@ -4732,6 +5702,26 @@
         </is>
       </c>
       <c r="P56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T56" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4740,37 +5730,35 @@
     <row r="57">
       <c r="A57" s="10" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="B57" s="11" t="inlineStr">
         <is>
-          <t>D.Y.Patil Education Societys,D.Y.Patil Technical Campus, Faculty of Engineering &amp; Faculty of Management,Talsande,Kolhapur.</t>
+          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
         </is>
       </c>
       <c r="C57" s="10" t="inlineStr">
         <is>
-          <t>678024210</t>
+          <t>627224610</t>
         </is>
       </c>
       <c r="D57" s="10" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>87.19</v>
+        <v>93.2</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>82.56999999999999</v>
+        <v>93.09</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>86.63</v>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>91.83</v>
+      </c>
+      <c r="H57" s="12" t="n">
+        <v>92.75</v>
       </c>
       <c r="I57" s="10" t="inlineStr">
         <is>
@@ -4808,6 +5796,26 @@
         </is>
       </c>
       <c r="P57" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q57" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R57" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T57" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4816,37 +5824,35 @@
     <row r="58">
       <c r="A58" s="7" t="inlineStr">
         <is>
-          <t>6780</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>D.Y.Patil Education Societys,D.Y.Patil Technical Campus, Faculty of Engineering &amp; Faculty of Management,Talsande,Kolhapur.</t>
+          <t>Dr. D. Y. Patil Pratishthans D.Y.Patil College of Engineering Akurdi, Pune</t>
         </is>
       </c>
       <c r="C58" s="7" t="inlineStr">
         <is>
-          <t>678091210</t>
+          <t>627299510</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Data Science)</t>
+          <t>Artificial Intelligence and Data Science</t>
         </is>
       </c>
       <c r="E58" s="9" t="n">
-        <v>86.45999999999999</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F58" s="9" t="n">
-        <v>81.89</v>
+        <v>92.41</v>
       </c>
       <c r="G58" s="9" t="n">
-        <v>86.23</v>
-      </c>
-      <c r="H58" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>91.41</v>
+      </c>
+      <c r="H58" s="9" t="n">
+        <v>92.40000000000001</v>
       </c>
       <c r="I58" s="7" t="inlineStr">
         <is>
@@ -4884,6 +5890,26 @@
         </is>
       </c>
       <c r="P58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T58" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4892,37 +5918,35 @@
     <row r="59">
       <c r="A59" s="10" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="B59" s="11" t="inlineStr">
         <is>
-          <t>Dr. D Y Patil Pratishthans College of Engineering, Kolhapur</t>
+          <t>MKSSS's Cummins College of Engineering for Women, Karvenagar,Pune</t>
         </is>
       </c>
       <c r="C59" s="10" t="inlineStr">
         <is>
-          <t>683924210</t>
+          <t>627624550</t>
         </is>
       </c>
       <c r="D59" s="10" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>87.61</v>
+        <v>96.06</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>79.48999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>87.09</v>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>95.12</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>95.88</v>
       </c>
       <c r="I59" s="10" t="inlineStr">
         <is>
@@ -4960,6 +5984,26 @@
         </is>
       </c>
       <c r="P59" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q59" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R59" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T59" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -4968,37 +6012,35 @@
     <row r="60">
       <c r="A60" s="7" t="inlineStr">
         <is>
-          <t>6839</t>
+          <t>6276</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Dr. D Y Patil Pratishthans College of Engineering, Kolhapur</t>
+          <t>MKSSS's Cummins College of Engineering for Women, Karvenagar,Pune</t>
         </is>
       </c>
       <c r="C60" s="7" t="inlineStr">
         <is>
-          <t>683991210</t>
+          <t>627624650</t>
         </is>
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>Computer Science and Engineering(Data Science)</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E60" s="9" t="n">
-        <v>86.69</v>
+        <v>95.47</v>
       </c>
       <c r="F60" s="9" t="n">
-        <v>79.09</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="G60" s="9" t="n">
-        <v>86.56999999999999</v>
-      </c>
-      <c r="H60" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>94.91</v>
+      </c>
+      <c r="H60" s="9" t="n">
+        <v>95.47</v>
       </c>
       <c r="I60" s="7" t="inlineStr">
         <is>
@@ -5036,6 +6078,26 @@
         </is>
       </c>
       <c r="P60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T60" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5044,17 +6106,17 @@
     <row r="61">
       <c r="A61" s="10" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="B61" s="11" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Technical Campus, Varale, Talegaon, Pune</t>
+          <t>International Institute of Information Technology (I²IT), Pune.</t>
         </is>
       </c>
       <c r="C61" s="10" t="inlineStr">
         <is>
-          <t>699124510</t>
+          <t>675424510</t>
         </is>
       </c>
       <c r="D61" s="10" t="inlineStr">
@@ -5063,20 +6125,16 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>86.45999999999999</v>
+        <v>91.77</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>86.51000000000001</v>
-      </c>
-      <c r="G61" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>91.70999999999999</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="H61" s="12" t="n">
+        <v>91.66</v>
       </c>
       <c r="I61" s="10" t="inlineStr">
         <is>
@@ -5114,6 +6172,26 @@
         </is>
       </c>
       <c r="P61" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q61" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R61" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T61" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5122,39 +6200,35 @@
     <row r="62">
       <c r="A62" s="7" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6754</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Technical Campus, Varale, Talegaon, Pune</t>
+          <t>International Institute of Information Technology (I²IT), Pune.</t>
         </is>
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>699156610</t>
+          <t>675424610</t>
         </is>
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>Computer Science</t>
+          <t>Information Technology</t>
         </is>
       </c>
       <c r="E62" s="9" t="n">
-        <v>85.41</v>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>91.48999999999999</v>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>91.43000000000001</v>
       </c>
       <c r="G62" s="9" t="n">
-        <v>84.86</v>
-      </c>
-      <c r="H62" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>88.97</v>
+      </c>
+      <c r="H62" s="9" t="n">
+        <v>91.37</v>
       </c>
       <c r="I62" s="7" t="inlineStr">
         <is>
@@ -5192,6 +6266,26 @@
         </is>
       </c>
       <c r="P62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T62" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5200,39 +6294,35 @@
     <row r="63">
       <c r="A63" s="10" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="B63" s="11" t="inlineStr">
         <is>
-          <t>Dr. D.Y. Patil Technical Campus, Varale, Talegaon, Pune</t>
+          <t>JSPM Narhe Technical Campus, Pune.</t>
         </is>
       </c>
       <c r="C63" s="10" t="inlineStr">
         <is>
-          <t>699184410</t>
+          <t>675524510</t>
         </is>
       </c>
       <c r="D63" s="10" t="inlineStr">
         <is>
-          <t>Electronics and Computer Engineering</t>
+          <t>Computer Engineering</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>82.65000000000001</v>
-      </c>
-      <c r="F63" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>90</v>
+      </c>
+      <c r="F63" s="12" t="n">
+        <v>89.63</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>82.17</v>
-      </c>
-      <c r="H63" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>84.38</v>
+      </c>
+      <c r="H63" s="12" t="n">
+        <v>89.76000000000001</v>
       </c>
       <c r="I63" s="10" t="inlineStr">
         <is>
@@ -5270,6 +6360,26 @@
         </is>
       </c>
       <c r="P63" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q63" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R63" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T63" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5278,74 +6388,850 @@
     <row r="64">
       <c r="A64" s="7" t="inlineStr">
         <is>
+          <t>6755</t>
+        </is>
+      </c>
+      <c r="B64" s="8" t="inlineStr">
+        <is>
+          <t>JSPM Narhe Technical Campus, Pune.</t>
+        </is>
+      </c>
+      <c r="C64" s="7" t="inlineStr">
+        <is>
+          <t>675526310</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence (AI) and Data Science</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="n">
+        <v>89.26000000000001</v>
+      </c>
+      <c r="F64" s="9" t="n">
+        <v>89.63</v>
+      </c>
+      <c r="G64" s="9" t="n">
+        <v>83.47</v>
+      </c>
+      <c r="H64" s="9" t="n">
+        <v>89.09</v>
+      </c>
+      <c r="I64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T64" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="10" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>D.Y.Patil Education Societys,D.Y.Patil Technical Campus, Faculty of Engineering &amp; Faculty of Management,Talsande,Kolhapur.</t>
+        </is>
+      </c>
+      <c r="C65" s="10" t="inlineStr">
+        <is>
+          <t>678024210</t>
+        </is>
+      </c>
+      <c r="D65" s="10" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E65" s="12" t="n">
+        <v>87.19</v>
+      </c>
+      <c r="F65" s="12" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>82.56999999999999</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>86.63</v>
+      </c>
+      <c r="I65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T65" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>6780</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>D.Y.Patil Education Societys,D.Y.Patil Technical Campus, Faculty of Engineering &amp; Faculty of Management,Talsande,Kolhapur.</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>678091210</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering(Data Science)</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="F66" s="9" t="n">
+        <v>85.72</v>
+      </c>
+      <c r="G66" s="9" t="n">
+        <v>81.89</v>
+      </c>
+      <c r="H66" s="9" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T66" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="10" t="inlineStr">
+        <is>
+          <t>6839</t>
+        </is>
+      </c>
+      <c r="B67" s="11" t="inlineStr">
+        <is>
+          <t>Dr. D Y Patil Pratishthans College of Engineering, Kolhapur</t>
+        </is>
+      </c>
+      <c r="C67" s="10" t="inlineStr">
+        <is>
+          <t>683924210</t>
+        </is>
+      </c>
+      <c r="D67" s="10" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>86.17</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>87.09</v>
+      </c>
+      <c r="I67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T67" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="inlineStr">
+        <is>
+          <t>6839</t>
+        </is>
+      </c>
+      <c r="B68" s="8" t="inlineStr">
+        <is>
+          <t>Dr. D Y Patil Pratishthans College of Engineering, Kolhapur</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>683991210</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>Computer Science and Engineering(Data Science)</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="n">
+        <v>86.69</v>
+      </c>
+      <c r="F68" s="9" t="n">
+        <v>86.06</v>
+      </c>
+      <c r="G68" s="9" t="n">
+        <v>79.09</v>
+      </c>
+      <c r="H68" s="9" t="n">
+        <v>86.56999999999999</v>
+      </c>
+      <c r="I68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T68" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
           <t>6991</t>
         </is>
       </c>
-      <c r="B64" s="8" t="inlineStr">
+      <c r="B69" s="11" t="inlineStr">
         <is>
           <t>Dr. D.Y. Patil Technical Campus, Varale, Talegaon, Pune</t>
         </is>
       </c>
-      <c r="C64" s="7" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>699124510</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>Computer Engineering</t>
+        </is>
+      </c>
+      <c r="E69" s="12" t="n">
+        <v>86.45999999999999</v>
+      </c>
+      <c r="F69" s="12" t="n">
+        <v>86.73999999999999</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="H69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T69" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t>6991</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>Dr. D.Y. Patil Technical Campus, Varale, Talegaon, Pune</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
+        <is>
+          <t>699156610</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Computer Science</t>
+        </is>
+      </c>
+      <c r="E70" s="9" t="n">
+        <v>85.41</v>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>85.06</v>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H70" s="9" t="n">
+        <v>84.86</v>
+      </c>
+      <c r="I70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T70" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="10" t="inlineStr">
+        <is>
+          <t>6991</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="inlineStr">
+        <is>
+          <t>Dr. D.Y. Patil Technical Campus, Varale, Talegaon, Pune</t>
+        </is>
+      </c>
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>699184410</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>Electronics and Computer Engineering</t>
+        </is>
+      </c>
+      <c r="E71" s="12" t="n">
+        <v>82.65000000000001</v>
+      </c>
+      <c r="F71" s="12" t="n">
+        <v>82.51000000000001</v>
+      </c>
+      <c r="G71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>82.17</v>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T71" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="inlineStr">
+        <is>
+          <t>6991</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>Dr. D.Y. Patil Technical Campus, Varale, Talegaon, Pune</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>699199510</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
+      <c r="D72" s="7" t="inlineStr">
         <is>
           <t>Artificial Intelligence and Data Science</t>
         </is>
       </c>
-      <c r="E64" s="9" t="n">
+      <c r="E72" s="9" t="n">
         <v>85.77</v>
       </c>
-      <c r="F64" s="9" t="n">
+      <c r="F72" s="9" t="n">
+        <v>85.43000000000001</v>
+      </c>
+      <c r="G72" s="9" t="n">
         <v>79.94</v>
       </c>
-      <c r="G64" s="9" t="n">
+      <c r="H72" s="9" t="n">
         <v>85.54000000000001</v>
       </c>
-      <c r="H64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O64" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P64" s="7" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S72" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T72" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -5353,14 +7239,14 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="H1:J1"/>
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="I1:L1"/>
+    <mergeCell ref="M1:P1"/>
+    <mergeCell ref="Q1:T1"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="D1:D2"/>
-    <mergeCell ref="N1:P1"/>
-    <mergeCell ref="K1:M1"/>
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="E1:H1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
